--- a/input/Studies/MEET2/WellsTest.xlsx
+++ b/input/Studies/MEET2/WellsTest.xlsx
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K2" s="16" t="inlineStr">
         <is>
-          <t>Production\FlashFractions\FlashFractionsTest.csv</t>
+          <t>Production/FlashFractions/FlashFractionsTest.csv</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="K3" s="16" t="inlineStr">
         <is>
-          <t>Production\FlashFractions\FlashFractionsTest.csv</t>
+          <t>Production/FlashFractions/FlashFractionsTest.csv</t>
         </is>
       </c>
       <c r="L3" t="n">
